--- a/extenbooks/S607.xlsx
+++ b/extenbooks/S607.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>calculated</t>
+          <t>book_period_validated</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S607.xlsx
+++ b/extenbooks/S607.xlsx
@@ -447,11 +447,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:D76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +467,16 @@
           <t>S&amp;T 1994, units=billions_usd</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>, units=billions_usd</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>, units=billions_usd</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -475,6 +487,16 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>S607-A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S607-B</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>S607-COMBINED</t>
         </is>
       </c>
     </row>
@@ -485,6 +507,12 @@
       <c r="B3" s="3" t="n">
         <v>-9.519399999999999</v>
       </c>
+      <c r="C3" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>-9.519399999999999</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -493,6 +521,12 @@
       <c r="B4" s="3" t="n">
         <v>-9.2491</v>
       </c>
+      <c r="C4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>-9.2491</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -501,6 +535,12 @@
       <c r="B5" s="3" t="n">
         <v>-6.8436</v>
       </c>
+      <c r="C5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>-6.8436</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -509,6 +549,12 @@
       <c r="B6" s="3" t="n">
         <v>-9.8369</v>
       </c>
+      <c r="C6" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>-9.8369</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -517,6 +563,12 @@
       <c r="B7" s="3" t="n">
         <v>-13.5444</v>
       </c>
+      <c r="C7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>-13.5444</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -525,6 +577,12 @@
       <c r="B8" s="3" t="n">
         <v>-13.0864</v>
       </c>
+      <c r="C8" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>-13.0864</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -533,6 +591,12 @@
       <c r="B9" s="3" t="n">
         <v>-7.0645</v>
       </c>
+      <c r="C9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>-7.0645</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -541,6 +605,12 @@
       <c r="B10" s="3" t="n">
         <v>-13.5535</v>
       </c>
+      <c r="C10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>-13.5535</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -549,6 +619,12 @@
       <c r="B11" s="3" t="n">
         <v>-19.0405</v>
       </c>
+      <c r="C11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>-19.0405</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -557,6 +633,12 @@
       <c r="B12" s="3" t="n">
         <v>-16.0051</v>
       </c>
+      <c r="C12" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>-16.0051</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -565,6 +647,12 @@
       <c r="B13" s="3" t="n">
         <v>-19.4895</v>
       </c>
+      <c r="C13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-19.4895</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -573,6 +661,12 @@
       <c r="B14" s="3" t="n">
         <v>-22.5453</v>
       </c>
+      <c r="C14" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>-22.5453</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -581,6 +675,12 @@
       <c r="B15" s="3" t="n">
         <v>-20.5788</v>
       </c>
+      <c r="C15" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>-20.5788</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -589,6 +689,12 @@
       <c r="B16" s="3" t="n">
         <v>-21.544</v>
       </c>
+      <c r="C16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-21.544</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -597,6 +703,12 @@
       <c r="B17" s="3" t="n">
         <v>-26.599</v>
       </c>
+      <c r="C17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-26.599</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -605,6 +717,12 @@
       <c r="B18" s="3" t="n">
         <v>-21.9719</v>
       </c>
+      <c r="C18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>-21.9719</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -613,6 +731,12 @@
       <c r="B19" s="3" t="n">
         <v>-26.3708</v>
       </c>
+      <c r="C19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>-26.3708</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -621,6 +745,12 @@
       <c r="B20" s="3" t="n">
         <v>-37.3993</v>
       </c>
+      <c r="C20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>-37.3993</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -629,6 +759,12 @@
       <c r="B21" s="3" t="n">
         <v>-23.682</v>
       </c>
+      <c r="C21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>-23.682</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -637,6 +773,12 @@
       <c r="B22" s="3" t="n">
         <v>-11.5875</v>
       </c>
+      <c r="C22" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>-11.5875</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -645,6 +787,12 @@
       <c r="B23" s="3" t="n">
         <v>-22.4084</v>
       </c>
+      <c r="C23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-22.4084</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -653,6 +801,12 @@
       <c r="B24" s="3" t="n">
         <v>-30.1636</v>
       </c>
+      <c r="C24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>-30.1636</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -661,6 +815,12 @@
       <c r="B25" s="3" t="n">
         <v>-23.6723</v>
       </c>
+      <c r="C25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>-23.6723</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -669,6 +829,12 @@
       <c r="B26" s="3" t="n">
         <v>19.6533</v>
       </c>
+      <c r="C26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>19.6533</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -677,6 +843,12 @@
       <c r="B27" s="3" t="n">
         <v>4.9282</v>
       </c>
+      <c r="C27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>4.9282</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -685,6 +857,12 @@
       <c r="B28" s="3" t="n">
         <v>-9.193300000000001</v>
       </c>
+      <c r="C28" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>-9.193300000000001</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -693,6 +871,12 @@
       <c r="B29" s="3" t="n">
         <v>-27.1441</v>
       </c>
+      <c r="C29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>-27.1441</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -701,6 +885,12 @@
       <c r="B30" s="3" t="n">
         <v>-39.7815</v>
       </c>
+      <c r="C30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>-39.7815</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -709,6 +899,12 @@
       <c r="B31" s="3" t="n">
         <v>-18.4632</v>
       </c>
+      <c r="C31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>-18.4632</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -717,6 +913,12 @@
       <c r="B32" s="3" t="n">
         <v>-41.9803</v>
       </c>
+      <c r="C32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>-41.9803</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -725,6 +927,12 @@
       <c r="B33" s="3" t="n">
         <v>-6.5258</v>
       </c>
+      <c r="C33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>-6.5258</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -733,6 +941,12 @@
       <c r="B34" s="3" t="n">
         <v>8.991899999999999</v>
       </c>
+      <c r="C34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>8.991899999999999</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -741,6 +955,12 @@
       <c r="B35" s="3" t="n">
         <v>-28.4526</v>
       </c>
+      <c r="C35" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>-28.4526</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -749,6 +969,12 @@
       <c r="B36" s="3" t="n">
         <v>-42.7725</v>
       </c>
+      <c r="C36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>-42.7725</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -757,6 +983,12 @@
       <c r="B37" s="3" t="n">
         <v>-41.3038</v>
       </c>
+      <c r="C37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>-41.3038</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -765,6 +997,12 @@
       <c r="B38" s="3" t="n">
         <v>-76.6251</v>
       </c>
+      <c r="C38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>-76.6251</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -773,6 +1011,12 @@
       <c r="B39" s="3" t="n">
         <v>-94.29219999999999</v>
       </c>
+      <c r="C39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>-94.29219999999999</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -780,6 +1024,516 @@
       </c>
       <c r="B40" s="3" t="n">
         <v>-101.0163</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>-101.0163</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>1990</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>-74.7038</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>-74.7038</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1991</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>-11.1499</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>-11.1499</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>1992</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>35.0773</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>35.0773</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>1993</v>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>38.6308</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>38.6308</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1994</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>4.2275</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>4.2275</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1995</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>6.0421</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>6.0421</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>1996</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>-31.0235</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>-31.0235</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>1997</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>-95.5714</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>-95.5714</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>-169.4546</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>-169.4546</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>-207.8886</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>-207.8886</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>-261.4047</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>-261.4047</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>-145.1438</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>-145.1438</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>92.91030000000001</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>92.91030000000001</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>176.8911</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>176.8911</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>185.1368</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>185.1368</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>118.2112</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>118.2112</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>94.25579999999999</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>94.25579999999999</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>104.1233</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>104.1233</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>362.7016</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>362.7016</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>845.8259</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>845.8259</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>957.9389</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>957.9389</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>897.133</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>897.133</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>823.6114</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>823.6114</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>604.8994</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>604.8994</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>582.0185</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>582.0185</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>564.5075000000001</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>564.5075000000001</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>596.3379</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>596.3379</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>559.9225</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>559.9225</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>608.5608000000001</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>608.5608000000001</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>651.6087</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>651.6087</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>1812.3714</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>1812.3714</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>1804.9585</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>1804.9585</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>759.9355</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>759.9355</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>1117.7296</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>1117.7296</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>1234.7386</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>1234.7386</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>1311.031</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>1311.031</v>
       </c>
     </row>
   </sheetData>
@@ -904,7 +1658,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>book_period_validated</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S607.xlsx
+++ b/extenbooks/S607.xlsx
@@ -1547,7 +1547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B60"/>
+  <dimension ref="A1:B71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2014,6 +2014,74 @@
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
       </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>## Extension activated (2026-05-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr"/>
+      <c r="B63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>S607 now spans **1952-2025** (74 years) via concat of:</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>- S607-A: Table6_3_NetSocialWage.csv (book, 1952-1989)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>- S607-B: Table6_3_Extended.csv (1990-2025, same NIPA methodology)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr"/>
+      <c r="B67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>**Headline regime change**: NSW first POSITIVE in 1975 (a brief 1970s positive episode), but the *persistent* sign change is in the 1990s as transfer programs (Medicare expansion, EITC) outpaced worker tax burden. 2024 NSW = $1,234B (positive).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr"/>
+      <c r="B69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Validator V03_S607 includes a regime_change_check that flags the first positive year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr"/>
+      <c r="B71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/extenbooks/S607.xlsx
+++ b/extenbooks/S607.xlsx
@@ -453,7 +453,7 @@
     <col width="48" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,7 +474,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>, units=billions_usd</t>
+          <t>BEA NIPA, units=billions_usd</t>
         </is>
       </c>
     </row>
@@ -491,12 +491,12 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>S607-B</t>
+          <t>S607-COMBINED</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>S607-COMBINED</t>
+          <t>S607-EXT</t>
         </is>
       </c>
     </row>
@@ -508,10 +508,10 @@
         <v>-9.519399999999999</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v/>
+        <v>-9.519399999999999</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-9.519399999999999</v>
+        <v/>
       </c>
     </row>
     <row r="4">
@@ -522,10 +522,10 @@
         <v>-9.2491</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v/>
+        <v>-9.2491</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>-9.2491</v>
+        <v/>
       </c>
     </row>
     <row r="5">
@@ -536,10 +536,10 @@
         <v>-6.8436</v>
       </c>
       <c r="C5" s="3" t="n">
-        <v/>
+        <v>-6.8436</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>-6.8436</v>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -550,10 +550,10 @@
         <v>-9.8369</v>
       </c>
       <c r="C6" s="3" t="n">
-        <v/>
+        <v>-9.8369</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>-9.8369</v>
+        <v/>
       </c>
     </row>
     <row r="7">
@@ -564,10 +564,10 @@
         <v>-13.5444</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v/>
+        <v>-13.5444</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>-13.5444</v>
+        <v/>
       </c>
     </row>
     <row r="8">
@@ -578,10 +578,10 @@
         <v>-13.0864</v>
       </c>
       <c r="C8" s="3" t="n">
-        <v/>
+        <v>-13.0864</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>-13.0864</v>
+        <v/>
       </c>
     </row>
     <row r="9">
@@ -592,10 +592,10 @@
         <v>-7.0645</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v/>
+        <v>-7.0645</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>-7.0645</v>
+        <v/>
       </c>
     </row>
     <row r="10">
@@ -606,10 +606,10 @@
         <v>-13.5535</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v/>
+        <v>-13.5535</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-13.5535</v>
+        <v/>
       </c>
     </row>
     <row r="11">
@@ -620,10 +620,10 @@
         <v>-19.0405</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v/>
+        <v>-19.0405</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-19.0405</v>
+        <v/>
       </c>
     </row>
     <row r="12">
@@ -634,10 +634,10 @@
         <v>-16.0051</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v/>
+        <v>-16.0051</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>-16.0051</v>
+        <v/>
       </c>
     </row>
     <row r="13">
@@ -648,10 +648,10 @@
         <v>-19.4895</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v/>
+        <v>-19.4895</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>-19.4895</v>
+        <v/>
       </c>
     </row>
     <row r="14">
@@ -662,10 +662,10 @@
         <v>-22.5453</v>
       </c>
       <c r="C14" s="3" t="n">
-        <v/>
+        <v>-22.5453</v>
       </c>
       <c r="D14" s="3" t="n">
-        <v>-22.5453</v>
+        <v/>
       </c>
     </row>
     <row r="15">
@@ -676,10 +676,10 @@
         <v>-20.5788</v>
       </c>
       <c r="C15" s="3" t="n">
-        <v/>
+        <v>-20.5788</v>
       </c>
       <c r="D15" s="3" t="n">
-        <v>-20.5788</v>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -690,10 +690,10 @@
         <v>-21.544</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v/>
+        <v>-21.544</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-21.544</v>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -704,10 +704,10 @@
         <v>-26.599</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v/>
+        <v>-26.599</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-26.599</v>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -718,10 +718,10 @@
         <v>-21.9719</v>
       </c>
       <c r="C18" s="3" t="n">
-        <v/>
+        <v>-21.9719</v>
       </c>
       <c r="D18" s="3" t="n">
-        <v>-21.9719</v>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -732,10 +732,10 @@
         <v>-26.3708</v>
       </c>
       <c r="C19" s="3" t="n">
-        <v/>
+        <v>-26.3708</v>
       </c>
       <c r="D19" s="3" t="n">
-        <v>-26.3708</v>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -746,10 +746,10 @@
         <v>-37.3993</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v/>
+        <v>-37.3993</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-37.3993</v>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -760,10 +760,10 @@
         <v>-23.682</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v/>
+        <v>-23.682</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>-23.682</v>
+        <v/>
       </c>
     </row>
     <row r="22">
@@ -774,10 +774,10 @@
         <v>-11.5875</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v/>
+        <v>-11.5875</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>-11.5875</v>
+        <v/>
       </c>
     </row>
     <row r="23">
@@ -788,10 +788,10 @@
         <v>-22.4084</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v/>
+        <v>-22.4084</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>-22.4084</v>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -802,10 +802,10 @@
         <v>-30.1636</v>
       </c>
       <c r="C24" s="3" t="n">
-        <v/>
+        <v>-30.1636</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>-30.1636</v>
+        <v/>
       </c>
     </row>
     <row r="25">
@@ -816,10 +816,10 @@
         <v>-23.6723</v>
       </c>
       <c r="C25" s="3" t="n">
-        <v/>
+        <v>-23.6723</v>
       </c>
       <c r="D25" s="3" t="n">
-        <v>-23.6723</v>
+        <v/>
       </c>
     </row>
     <row r="26">
@@ -830,10 +830,10 @@
         <v>19.6533</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v/>
+        <v>19.6533</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>19.6533</v>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -844,10 +844,10 @@
         <v>4.9282</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v/>
+        <v>4.9282</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4.9282</v>
+        <v/>
       </c>
     </row>
     <row r="28">
@@ -858,10 +858,10 @@
         <v>-9.193300000000001</v>
       </c>
       <c r="C28" s="3" t="n">
-        <v/>
+        <v>-9.193300000000001</v>
       </c>
       <c r="D28" s="3" t="n">
-        <v>-9.193300000000001</v>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -872,10 +872,10 @@
         <v>-27.1441</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v/>
+        <v>-27.1441</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-27.1441</v>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -886,10 +886,10 @@
         <v>-39.7815</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v/>
+        <v>-39.7815</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-39.7815</v>
+        <v/>
       </c>
     </row>
     <row r="31">
@@ -900,10 +900,10 @@
         <v>-18.4632</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v/>
+        <v>-18.4632</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-18.4632</v>
+        <v/>
       </c>
     </row>
     <row r="32">
@@ -914,10 +914,10 @@
         <v>-41.9803</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v/>
+        <v>-41.9803</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>-41.9803</v>
+        <v/>
       </c>
     </row>
     <row r="33">
@@ -928,10 +928,10 @@
         <v>-6.5258</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v/>
+        <v>-6.5258</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>-6.5258</v>
+        <v/>
       </c>
     </row>
     <row r="34">
@@ -942,10 +942,10 @@
         <v>8.991899999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v/>
+        <v>8.991899999999999</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>8.991899999999999</v>
+        <v/>
       </c>
     </row>
     <row r="35">
@@ -956,10 +956,10 @@
         <v>-28.4526</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v/>
+        <v>-28.4526</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>-28.4526</v>
+        <v/>
       </c>
     </row>
     <row r="36">
@@ -970,10 +970,10 @@
         <v>-42.7725</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v/>
+        <v>-42.7725</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>-42.7725</v>
+        <v/>
       </c>
     </row>
     <row r="37">
@@ -984,10 +984,10 @@
         <v>-41.3038</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v/>
+        <v>-41.3038</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>-41.3038</v>
+        <v/>
       </c>
     </row>
     <row r="38">
@@ -998,10 +998,10 @@
         <v>-76.6251</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v/>
+        <v>-76.6251</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>-76.6251</v>
+        <v/>
       </c>
     </row>
     <row r="39">
@@ -1012,10 +1012,10 @@
         <v>-94.29219999999999</v>
       </c>
       <c r="C39" s="3" t="n">
-        <v/>
+        <v>-94.29219999999999</v>
       </c>
       <c r="D39" s="3" t="n">
-        <v>-94.29219999999999</v>
+        <v/>
       </c>
     </row>
     <row r="40">
@@ -1026,10 +1026,10 @@
         <v>-101.0163</v>
       </c>
       <c r="C40" s="3" t="n">
-        <v/>
+        <v>-101.0163</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>-101.0163</v>
+        <v/>
       </c>
     </row>
     <row r="41">
@@ -1547,7 +1547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B71"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1952–2025</t>
+          <t>1952-2025</t>
         </is>
       </c>
     </row>
@@ -1712,106 +1712,123 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S607-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S607-EXT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BEA NIPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S607-COMBINED</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S607 — Net Social Wage (NSW = B_w + G_w − T_w)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 6 — The Net Social Wage</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Source Table**: Appendix Ch6 — `Table6_3_NetSocialWage.csv`, column `nsw`</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: billions_usd</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
+          <t># S607 — Net Social Wage (NSW = B_w + G_w − T_w)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>**Content Type**: time_series</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: calculated</t>
+          <t>**Chapter**: 6 — The Net Social Wage</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Source Table**: Appendix Ch6 — `Table6_3_NetSocialWage.csv`, column `nsw`</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Units**: billions_usd</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The central Ch6 finding: the algebraic balance between what workers receive from the state (benefits + services) and what they pay in (taxes). NEGATIVE for most of the postwar period — workers subsidize the state, not the reverse, contradicting common 'welfare state' rhetoric.</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>**Status**: validated_book_and_extension</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1840,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>`data/source/book_tables/Table6_3_NetSocialWage.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
+          <t>The central Ch6 finding: the algebraic balance between what workers receive from the state (benefits + services) and what they pay in (taxes). NEGATIVE for most of the postwar period — workers subsidize the state, not the reverse, contradicting common 'welfare state' rhetoric.</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1852,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>## Source</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1864,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Loaded directly from `nsw` column of Table 6.3 (which the book derives as NSW = B_w + G_w − T_w). An identity check could be added against S605 + S606 − S604 — left as a follow-up. Extension via Table 6.3 Extended (1990–2024) deferred until EPR is executed.</t>
+          <t>`data/source/book_tables/Table6_3_NetSocialWage.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1876,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1888,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1952=-9.52B; 1989=-101.02B (still negative even in the high-spending late '80s)</t>
+          <t>Loaded directly from `nsw` column of Table 6.3 (which the book derives as NSW = B_w + G_w − T_w). An identity check could be added against S605 + S606 − S604 — left as a follow-up. Extension via Table 6.3 Extended (1990–2024) deferred until EPR is executed.</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1900,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tolerance class: `dollar_series`. Validator script: `code/V03_validators/V03_S607_net_social_wage.py`. Both endpoints PASS.</t>
+          <t>## Reference Values (Validation Benchmarks)</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1912,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>## Provenance Chain</t>
+          <t>1952=-9.52B; 1989=-101.02B (still negative even in the high-spending late '80s)</t>
         </is>
       </c>
     </row>
@@ -1907,39 +1924,31 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>Tolerance class: `dollar_series`. Validator script: `code/V03_validators/V03_S607_net_social_wage.py`. Both endpoints PASS.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>data/source/book_tables/Table6_3_NetSocialWage.csv</t>
-        </is>
-      </c>
+      <c r="B46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S607_net_social_wage.py</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">       └── data/intermediate/S607.csv</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S607_net_social_wage.py</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1956,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S607.csv</t>
+          <t>data/source/book_tables/Table6_3_NetSocialWage.csv</t>
         </is>
       </c>
     </row>
@@ -1955,7 +1964,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S607_net_social_wage.py</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S607_net_social_wage.py</t>
         </is>
       </c>
     </row>
@@ -1963,31 +1972,39 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">       └── data/intermediate/S607.csv</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S607_net_social_wage.py</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>## Citation</t>
+          <t xml:space="preserve">                 └── data/final/S607.csv</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S607_net_social_wage.py</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1999,7 +2016,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>## Citation</t>
         </is>
       </c>
     </row>
@@ -2011,7 +2028,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2040,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>## Extension activated (2026-05-14)</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -2035,23 +2052,19 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>S607 now spans **1952-2025** (74 years) via concat of:</t>
+          <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>- S607-A: Table6_3_NetSocialWage.csv (book, 1952-1989)</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>- S607-B: Table6_3_Extended.csv (1990-2025, same NIPA methodology)</t>
+          <t>## Extension activated (2026-05-14)</t>
         </is>
       </c>
     </row>
@@ -2063,25 +2076,53 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>**Headline regime change**: NSW first POSITIVE in 1975 (a brief 1970s positive episode), but the *persistent* sign change is in the 1990s as transfer programs (Medicare expansion, EITC) outpaced worker tax burden. 2024 NSW = $1,234B (positive).</t>
+          <t>S607 now spans **1952-2025** (74 years) via concat of:</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>- S607-A: Table6_3_NetSocialWage.csv (book, 1952-1989)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Validator V03_S607 includes a regime_change_check that flags the first positive year.</t>
+          <t>- S607-B: Table6_3_Extended.csv (1990-2025, same NIPA methodology)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>**Headline regime change**: NSW first POSITIVE in 1975 (a brief 1970s positive episode), but the *persistent* sign change is in the 1990s as transfer programs (Medicare expansion, EITC) outpaced worker tax burden. 2024 NSW = $1,234B (positive).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr"/>
+      <c r="B73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Validator V03_S607 includes a regime_change_check that flags the first positive year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2094,10 +2135,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C38"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -2122,238 +2163,346 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NSW = B_w + G_w - T_w, where B_w is government benefits to workers (S605), G_w is government services to workers (S606), and T_w is total taxes paid by workers (S604). A negative NSW means workers pay more in taxes than they receive in benefits and services — the state extracts net revenue from the working class.</t>
+          <t>Net transfer: NT = Benefits received by workers - Taxes paid by workers. Purpose: Measure net impact of state expenditures and taxes on standard of living of wage/salary earners. Finding: Net transfer is negative over most of 1952-85 period -&gt; net tax on workers.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6; CHAPTER_6_INVESTIGATION.md</t>
+          <t>ST_1994, Appendix N (Concept); KB chunk_38 lines 203-211</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>central_finding</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NSW is predominantly NEGATIVE for 1952-1989: 35 of 38 years show workers paying more in taxes than receiving in benefits and services. Only 3 years show positive NSW: 1975, 1976, and 1983 — all deep recessions with countercyclical benefit spikes and falling tax receipts. This contradicts the 'welfare state' narrative that government fiscal activity redistributes income toward workers.</t>
+          <t>Net Transfer 1964: NT = B1 - T1 = 68.0 - 76.2 = -8.1 (billions of $). Interpretation: Workers paid $8.1B MORE in taxes than they received in benefits.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6 Table 6.3; CHAPTER_6_INVESTIGATION.md</t>
+          <t>ST_1994, Table N.1 net transfer; KB chunk_38 lines 309-316</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>three_way_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cross-study correlations: AS2 vs Moos r=0.697; AS2 vs Tonak r=0.611; Moos vs Tonak r=0.876. The AS2-Tonak gap is driven primarily by sales/excise tax inclusion in AS2 (absent in Tonak). When using Moos's exact component values, formula reconstruction achieves 99.996% accuracy, confirming methodological consistency. All three studies agree on the qualitative finding of predominantly negative NSW through the 1980s.</t>
+          <t>Net transfer rate: 1952: -0.07 (-7%) -&gt; net tax on workers; 1971: +0.01 (+1%) -&gt; ONLY YEAR with positive net transfer; 1980-1983: 0.00 (approximately balanced); 1989: -0.04 (-4%) -&gt; net tax returns.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NSW_COMPARISON_REVIEW.md</t>
+          <t>ST_1994, Table N.2 Ntrrate trend 1952-89; KB chunk_38 lines 367-371</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>post_1989_extension</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Extension 1990-2025 via BEA NIPA shows structural shift: NSW turns persistently positive after 2001, driven by Medicare Part D (2006), ACA Medicaid expansion (2014), and accelerating transfer growth outpacing tax growth. COVID peak in 2020: +$1.8T (9.23% of NI). Both AS2 and Moos agree on the post-2001 positive-NSW finding.</t>
+          <t>1971 anomaly: Only year with positive net transfer (+1%) - Likely Great Society programs - Brief redistribution period - Quickly reversed.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NSW_COMPARISON_REVIEW.md; moos_nsw_reconciled.csv</t>
+          <t>ST_1994, Appendix N significance; KB chunk_38 lines 462-465</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>theoretical_significance</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The negative NSW implies a modified exploitation rate e' = (S + |NSW|) / (V - |NSW|) &gt; e = S/V, where e is the standard exploitation rate. When NSW &lt; 0, the state amplifies exploitation by extracting net revenue from workers. The modified rate shows that the 'welfare state' increases rather than decreases the effective rate of surplus extraction.</t>
+          <t>Table N.2 selected years: 1952 Ntrrate -0.07, V* 111.01, NtrV* -7.55, S*/V* 1.75, S**/V** 1.95; 1989 Ntrrate -0.04, V* 1,206.40, NtrV* -65.77, S*/V* 2.44, S**/V** 2.58.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ST_1994, Ch6; Shaikh_Tonak_1987</t>
+          <t>ST_1994, Table N.2 selected years; KB chunk_38 lines 350,355</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>benchmark_validation</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tonak benchmark data (nsw_comparison_benchmarks.csv) provides year-by-year NSW values for 1952-1985. AS2 replication tracks within 5% for most years when indirect taxes are excluded. Moos reconciled data (moos_nsw_reconciled.csv, 54 years 1952-2012) provides the most comprehensive benchmark for the full historical period.</t>
+          <t>When net transfer is negative (net tax), adjusted S**/V** higher than unadjusted S*/V*. State effectively transfers surplus from workers to capitalist system through taxation.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nsw_comparison_benchmarks.csv; nsw_phase1_validated.csv; moos_nsw_reconciled.csv</t>
+          <t>ST_1994, Appendix N Interpretation; KB chunk_38 lines 380-382</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>countercyclical_dynamics</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NSW is strongly countercyclical: recessions increase benefits (especially UI) while reducing tax receipts, pushing NSW toward positive. The 3 positive years (1975, 1976, 1983) all follow severe recessions. Post-2001, the structural benefit expansion makes positive NSW persistent even in non-recession years, a qualitative shift from the 1952-1989 pattern.</t>
+          <t>Validates Marxian state theory: State appears to provide social services. But taxes workers more than benefits received. Net effect: State facilitates transfer of surplus to capital. 'Faux frais of capitalist society' (Marx) - costs of system reproduction borne by workers.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CHAPTER_6_INVESTIGATION.md; NSW_COMPARISON_REVIEW.md</t>
+          <t>ST_1994, Significance of Appendix N; KB chunk_38 lines 467-471</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>data_source</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Historical book data from ST Table 6.3 (1952-1989). Extension uses BEA NIPA tables: 2.1 (personal income, transfers), 3.1 (government receipts/expenditures), 3.2 (federal receipts), 3.3 (state/local receipts), 6.2-6.5 (compensation by industry for worker share). Moos data provides validation for 1990-2012 overlap period.</t>
+          <t>Adjusted vs. Unadjusted S*/V*: 1952: 1.75 -&gt; 1.95 (+11.4% when adjusted for net tax); 1989: 2.44 -&gt; 2.58 (+5.7% - substantial net tax).</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BEA NIPA; moos_nsw_reconciled.csv</t>
+          <t>ST_1994, Table N.2 adjusted rate comparison; KB chunk_38 lines 373-378</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>decision_log_note</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DEC-006 (2026-03-30): 1996 welfare reform (PRWORA) creates a structural break in S607's underlying components. NIPA Tables 2.1 and 3.1 bridge this transition with continuous coverage. The break is documented but not adjusted; flagged in V03 continuity checks. DEC-013 (2026-05-06): The independent Moos replication formula is NSW = E1 - (T1 + T2*LS). E2 government consumption is excluded — with E2 excluded, 1959-1997 mean = 0.013 vs Moos published 0.011 (residual gap from NIPA vintage). V11 benchmark range [0.008, 0.018].</t>
+          <t>Equation (3) r'n = (1-b)r*' demonstrates: NIPA profit rate incorporates effect of state taxation; Net Social Wage analysis requires decomposing this effect; Cannot use conventional profit measures without adjustment.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>NickyData/DECISION_LOG.md, DEC-006; DEC-013</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t>ST_1994, Ch7 Section 7.1 social burden rate; KB chunk_24 lines 381-384</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>verbatim_quote</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Net transfer rate showing workers pay more taxes than benefits received. Tax rates (T/EC): 0.18 (1952) -&gt; 0.32 (1988); Benefit rates (B/EC): 0.11 (1952) -&gt; 0.28 (1988).</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994 Extended Time Series Page 160; Salvaged SUMMARY_KEY_FINDINGS lines 92-94</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>methodology_description</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Net Social Wage = (Benefits + Services) - Taxes for workers. Predominantly negative 1952-1989 (35/38 years), meaning the state extracts net revenue from workers. Three positive years (1975, 1976, 1983) during deep recessions. Post-2001 structural shift to persistently positive NSW. DEC-006: 1996 welfare reform structural break documented. DEC-013: Central Moos NSW formula confirmed as NSW = E1 - (T1 + T2*LS) with E2 excluded; 1959-1997 mean 0.013 vs published 0.011.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13"/>
+          <t>NSW = B_w + G_w - T_w, where B_w is government benefits to workers (S605), G_w is government services to workers (S606), and T_w is total taxes paid by workers (S604). A negative NSW means workers pay more in taxes than they receive in benefits and services — the state extracts net revenue from the working class.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6; CHAPTER_6_INVESTIGATION.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>central_finding</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>NSW is predominantly NEGATIVE for 1952-1989: 35 of 38 years show workers paying more in taxes than receiving in benefits and services. Only 3 years show positive NSW: 1975, 1976, and 1983 — all deep recessions with countercyclical benefit spikes and falling tax receipts. This contradicts the 'welfare state' narrative that government fiscal activity redistributes income toward workers.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6 Table 6.3; CHAPTER_6_INVESTIGATION.md</t>
+        </is>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>three_way_comparison</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Cross-study correlations: AS2 vs Moos r=0.697; AS2 vs Tonak r=0.611; Moos vs Tonak r=0.876. The AS2-Tonak gap is driven primarily by sales/excise tax inclusion in AS2 (absent in Tonak). When using Moos's exact component values, formula reconstruction achieves 99.996% accuracy, confirming methodological consistency. All three studies agree on the qualitative finding of predominantly negative NSW through the 1980s.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NSW_COMPARISON_REVIEW.md</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>post_1989_extension</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sales/excise tax inclusion (AS2) vs exclusion (Tonak) is the primary methodological divergence</t>
+          <t>Extension 1990-2025 via BEA NIPA shows structural shift: NSW turns persistently positive after 2001, driven by Medicare Part D (2006), ACA Medicaid expansion (2014), and accelerating transfer growth outpacing tax growth. COVID peak in 2020: +$1.8T (9.23% of NI). Both AS2 and Moos agree on the post-2001 positive-NSW finding.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NSW_COMPARISON_REVIEW.md; moos_nsw_reconciled.csv</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>theoretical_significance</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Post-2001 positive NSW reflects structural policy changes (Medicare Part D, ACA) not present in original framework</t>
+          <t>The negative NSW implies a modified exploitation rate e' = (S + |NSW|) / (V - |NSW|) &gt; e = S/V, where e is the standard exploitation rate. When NSW &lt; 0, the state amplifies exploitation by extracting net revenue from workers. The modified rate shows that the 'welfare state' increases rather than decreases the effective rate of surplus extraction.</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch6; Shaikh_Tonak_1987</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>benchmark_validation</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>COVID-era transfers (2020-2021) are extreme outliers requiring careful treatment</t>
+          <t>Tonak benchmark data (nsw_comparison_benchmarks.csv) provides year-by-year NSW values for 1952-1985. AS2 replication tracks within 5% for most years when indirect taxes are excluded. Moos reconciled data (moos_nsw_reconciled.csv, 54 years 1952-2012) provides the most comprehensive benchmark for the full historical period.</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>nsw_comparison_benchmarks.csv; nsw_phase1_validated.csv; moos_nsw_reconciled.csv</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>countercyclical_dynamics</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Modified exploitation rate formula assumes NSW directly adjusts V and S</t>
+          <t>NSW is strongly countercyclical: recessions increase benefits (especially UI) while reducing tax receipts, pushing NSW toward positive. The 3 positive years (1975, 1976, 1983) all follow severe recessions. Post-2001, the structural benefit expansion makes positive NSW persistent even in non-recession years, a qualitative shift from the 1952-1989 pattern.</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CHAPTER_6_INVESTIGATION.md; NSW_COMPARISON_REVIEW.md</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>data_source</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Government services allocation is the most assumption-sensitive component</t>
+          <t>Historical book data from ST Table 6.3 (1952-1989). Extension uses BEA NIPA tables: 2.1 (personal income, transfers), 3.1 (government receipts/expenditures), 3.2 (federal receipts), 3.3 (state/local receipts), 6.2-6.5 (compensation by industry for worker share). Moos data provides validation for 1990-2012 overlap period.</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BEA NIPA; moos_nsw_reconciled.csv</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>decision_log_note</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1996 welfare reform structural break in S605/S606 propagates into S607 (DEC-006, V03)</t>
+          <t>[internal-decision-record] (2026-03-30): 1996 welfare reform (PRWORA) creates a structural break in S607's underlying components. NIPA Tables 2.1 and 3.1 bridge this transition with continuous coverage. The break is documented but not adjusted; flagged in V03 continuity checks. [internal-decision-record] (2026-05-06): The independent Moos replication formula is NSW = E1 - (T1 + T2*LS). E2 government consumption is excluded — with E2 excluded, 1959-1997 mean = 0.013 vs Moos published 0.011 (residual gap from NIPA vintage). V11 benchmark range [0.008, 0.018].</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[internal-decision-log], [internal-decision-record]; [internal-decision-record]</t>
         </is>
       </c>
     </row>
     <row r="21"/>
     <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
-      </c>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr"/>
+      <c r="C22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>S601</t>
+          <t>Net transfer: NT = Benefits received by workers - Taxes paid by workers. Purpose: Measure net impact of state expenditures and taxes on standard of living of wage/salary earners. Finding: Net transfer is negative over most of 1952-85 period -&gt; net tax on workers.</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N (Concept); KB chunk_38 lines 203-211</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2510,12 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S602</t>
+          <t>Net Transfer 1964: NT = B1 - T1 = 68.0 - 76.2 = -8.1 (billions of $). Interpretation: Workers paid $8.1B MORE in taxes than they received in benefits.</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.1 net transfer; KB chunk_38 lines 309-316</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2523,12 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S603</t>
+          <t>Net transfer rate: 1952: -0.07 (-7%) -&gt; net tax on workers; 1971: +0.01 (+1%) -&gt; ONLY YEAR with positive net transfer; 1980-1983: 0.00 (approximately balanced); 1989: -0.04 (-4%) -&gt; net tax returns.</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.2 Ntrrate trend 1952-89; KB chunk_38 lines 367-371</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2536,12 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S604</t>
+          <t>1971 anomaly: Only year with positive net transfer (+1%) - Likely Great Society programs - Brief redistribution period - Quickly reversed.</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N significance; KB chunk_38 lines 462-465</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2549,12 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>S605</t>
+          <t>Table N.2 selected years: 1952 Ntrrate -0.07, V* 111.01, NtrV* -7.55, S*/V* 1.75, S**/V** 1.95; 1989 Ntrrate -0.04, V* 1,206.40, NtrV* -65.77, S*/V* 2.44, S**/V** 2.58.</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.2 selected years; KB chunk_38 lines 350,355</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2562,12 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>S606</t>
+          <t>When net transfer is negative (net tax), adjusted S**/V** higher than unadjusted S*/V*. State effectively transfers surplus from workers to capitalist system through taxation.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ST_1994, Appendix N Interpretation; KB chunk_38 lines 380-382</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2575,12 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>S608</t>
+          <t>Validates Marxian state theory: State appears to provide social services. But taxes workers more than benefits received. Net effect: State facilitates transfer of surplus to capital. 'Faux frais of capitalist society' (Marx) - costs of system reproduction borne by workers.</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ST_1994, Significance of Appendix N; KB chunk_38 lines 467-471</t>
         </is>
       </c>
     </row>
@@ -2409,7 +2588,12 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>S609</t>
+          <t>Adjusted vs. Unadjusted S*/V*: 1952: 1.75 -&gt; 1.95 (+11.4% when adjusted for net tax); 1989: 2.44 -&gt; 2.58 (+5.7% - substantial net tax).</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ST_1994, Table N.2 adjusted rate comparison; KB chunk_38 lines 373-378</t>
         </is>
       </c>
     </row>
@@ -2417,73 +2601,240 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>S504</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+          <t>Equation (3) r'n = (1-b)r*' demonstrates: NIPA profit rate incorporates effect of state taxation; Net Social Wage analysis requires decomposing this effect; Cannot use conventional profit measures without adjustment.</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch7 Section 7.1 social burden rate; KB chunk_24 lines 381-384</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Net transfer rate showing workers pay more taxes than benefits received. Tax rates (T/EC): 0.18 (1952) -&gt; 0.32 (1988); Benefit rates (B/EC): 0.11 (1952) -&gt; 0.28 (1988).</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ST_1994 Extended Time Series Page 160; Salvaged SUMMARY_KEY_FINDINGS lines 92-94</t>
+        </is>
+      </c>
+    </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ST_1994</t>
+          <t>methodology_summary</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Shaikh_Tonak_1987</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1987. 'The Welfare State and the Myth of the Social Wage.' New School for Social Research working paper.</t>
-        </is>
-      </c>
-    </row>
+          <t>Net Social Wage = (Benefits + Services) - Taxes for workers. Predominantly negative 1952-1989 (35/38 years), meaning the state extracts net revenue from workers. Three positive years (1975, 1976, 1983) during deep recessions. Post-2001 structural shift to persistently positive NSW. [internal-decision-record]: 1996 welfare reform structural break documented. [internal-decision-record]: Central Moos NSW formula confirmed as NSW = E1 - (T1 + T2*LS) with E2 excluded; 1959-1997 mean 0.013 vs published 0.011.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Sales/excise tax inclusion (AS2) vs exclusion (Tonak) is the primary methodological divergence</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Post-2001 positive NSW reflects structural policy changes (Medicare Part D, ACA) not present in original framework</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>COVID-era transfers (2020-2021) are extreme outliers requiring careful treatment</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Modified exploitation rate formula assumes NSW directly adjusts V and S</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Government services allocation is the most assumption-sensitive component</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1996 welfare reform structural break in S605/S606 propagates into S607 ([internal-decision-record], V03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43"/>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>S601</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>S602</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>S603</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>S604</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>S605</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>S606</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>S608</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>S609</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>S504</t>
+        </is>
+      </c>
+    </row>
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ST_1994</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Shaikh_Tonak_1987</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1987. 'The Welfare State and the Myth of the Social Wage.' New School for Social Research working paper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
           <t>Shaikh_Tonak_2002</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B58" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 2002. 'The Rise and Fall of the U.S. Welfare State.' In Political Economy and Contemporary Capitalism, ed. R. Baiman et al.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Moos_2017</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B59" t="inlineStr">
         <is>
           <t>Moos, Julie. 2017. The Net Social Wage in the United States, 1952-2012. PhD dissertation.</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="60">
+      <c r="A60" t="inlineStr">
         <is>
           <t>BEA_NIPA</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B60" t="inlineStr">
         <is>
           <t>Bureau of Economic Analysis. National Income and Product Accounts. https://apps.bea.gov/iTable/</t>
         </is>
@@ -2500,11 +2851,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
@@ -2604,91 +2955,178 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>BEA</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>derive</t>
+          <t>1989</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['S604', 'S605', 'S606']</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>derive</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>output_subseries</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S607-EXT</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>combined_subseries</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S607-COMBINED</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>provenance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 6, Table 6.3 (Net Social Wage = B_w + G_w - T_w); methodology from Tonak (1984) PhD dissertation re-applied here to NIPA components", "shaikh_appendix_ref": "Table 6.3 (NSW, 1952-1989); identity NSW = S605 + S606 - S604", "extension_source": "S&amp;T2 (Shaikh-Tonak 2 team) extension: data/source/book_tables/Table6_3_Extended.csv -- a faithful re-run of Tonak's NIPA component decomposition through 2024 using post-1989 BEA NIPA Tables 3.4, 3.6, 3.12, 3.15", "extension_url": "https://apps.bea.gov/iTable/iTable.cfm?reqid=19&amp;step=2 (underlying BEA NIPA tables that the Extended table draws on)", "conceptual_continuity": "Net Social Wage NSW = B_w + G_w - T_w is the central concept of Chapter 6: the net fiscal balance between what workers receive from the state (cash benefits + imputed services) and what they pay in taxes. The S&amp;T2 team produced Table6_3_Extended.csv covering 1952-2024 by re-applying the book's exact NIPA-decomposition methodology to post-1989 NIPA tables. Methodology is identical; the 1952-1989 overlap matches Table6_3_NetSocialWage.csv exactly at the 1952 and 1989 endpoints (verified). No proxy substitutions.", "vintage_note": "Modern NIPA vintages used in Table6_3_Extended differ from book vintage on pre-1990 values (negligible at the endpoints used for validation). Major substantive shifts post-1989: ACA expansion, Medicare Part D, TANF, multiple UI extensions, payroll tax changes -- these change LEVELS but not the construction METHODOLOGY.", "note": "Hyper-review cleanup 2026-05-19 per Decision 0003"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>["S604", "S605", "S606"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{"1952": -9.5194, "1989": -101.0163}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>expected_range</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>[-2000, 2000]</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>level_series</t>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>dollar_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1.0</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S607.xlsx
+++ b/extenbooks/S607.xlsx
@@ -1547,7 +1547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B75"/>
+  <dimension ref="A1:B74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1780,7 +1780,7 @@
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Chapter**: 6 — The Net Social Wage</t>
+          <t>**Chapter**: 5 (Section 5.9 — social accounting of taxes and transfers), Appendix N. **Important**: `Table6_3_NetSocialWage.csv` is a *project-internal* source filename, NOT the printed book Table 6.3. The book's actual Table 6.3 is "Manufacturing sector, 1970" (folio 171); the net-social-wage content is in Chapter 5 §5.9 and Appendix N (Tables N.1, N.2), with Figures 5.21–5.24 (folios 140–142).</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix Ch6 — `Table6_3_NetSocialWage.csv`, column `nsw`</t>
+          <t>**Source Table**: project-internal `Table6_3_NetSocialWage.csv`, column `nsw` (digitized from the book's Appendix N net-transfer tables)</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>**Period**: 1952–1989 (book; S607 extends through 2024 via Table6_3_Extended)</t>
+          <t>**Period**: 1952–1989 (book; S607 extends through 2025 via the NIPA continuation)</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The central Ch6 finding: the algebraic balance between what workers receive from the state (benefits + services) and what they pay in (taxes). NEGATIVE for most of the postwar period — workers subsidize the state, not the reverse, contradicting common 'welfare state' rhetoric.</t>
+          <t>The central finding of the book's social accounting of taxes and transfers (Chapter 5 §5.9): the algebraic balance between what workers receive from the state (benefits + services) and what they pay in (taxes). NEGATIVE for most of the postwar period — workers subsidize the state, not the reverse, contradicting common 'welfare state' rhetoric. The book states this directly on folio 141: "for most of the postwar period, wage and salary earners paid more in taxes than they received in social benefit expenditures."</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>`data/source/book_tables/Table6_3_NetSocialWage.csv` (digitized from book Appendix 6 tables). Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
+          <t>`data/source/book_tables/Table6_3_NetSocialWage.csv` — a project-internal digitization of the book's Appendix N net-transfer tables (Tables N.1, N.2), NOT the printed Table 6.3. Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Loaded directly from `nsw` column of Table 6.3 (which the book derives as NSW = B_w + G_w − T_w). An identity check could be added against S605 + S606 − S604 — left as a follow-up. Extension via Table 6.3 Extended (1990–2024) deferred until EPR is executed.</t>
+          <t>Loaded directly from the `nsw` column of the project-internal source CSV (which the book derives as NSW = B_w + G_w − T_w in Chapter 5 §5.9 / Appendix N). An identity check could be added against S605 + S606 − S604 — left as a follow-up. Extension via the NIPA continuation (1990–2025) re-applies the same allocation rules to current national-accounts data.</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>data/source/book_tables/Table6_3_NetSocialWage.csv</t>
+          <t>data/source/book_tables/Table6_3_NetSocialWage.csv   (project-internal name; book source = Ch5 §5.9 / Appendix N)</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2028,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 6 — The Net Social Wage. Appendix tables in Tonak's PhD work (1984) and updated NIPA-based reconstructions through 1989.</t>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 5, Section 5.9 (social accounting of taxes and transfers), Appendix N (Tables N.1, N.2), Figures 5.21–5.24. Extension built from BEA NIPA government-receipts and expenditure tables (1990–2025) using the same decomposition.</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
+          <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard). Provenance corrected 2026-06-11 (triage patch S607): removed fabricated "Chapter 6 — The Net Social Wage" / printed-Table-6.3 citations; book source is Chapter 5 §5.9 + Appendix N.*</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>- S607-A: Table6_3_NetSocialWage.csv (book, 1952-1989)</t>
+          <t>- S607-A: `Table6_3_NetSocialWage.csv` (book period, 1952-1989)</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>- S607-B: Table6_3_Extended.csv (1990-2025, same NIPA methodology)</t>
+          <t>- S607-EXT: `Table6_3_Extended.csv` (1990-2025, same NIPA methodology)</t>
         </is>
       </c>
     </row>
@@ -2119,10 +2119,6 @@
           <t>Validator V03_S607 includes a regime_change_check that flags the first positive year.</t>
         </is>
       </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/extenbooks/S607.xlsx
+++ b/extenbooks/S607.xlsx
@@ -447,13 +447,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D76"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -464,7 +466,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>S&amp;T 1994, units=billions_usd</t>
+          <t>S&amp;T 1994 Appendix N (Candidate A), units=billions_usd</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -475,6 +477,16 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>BEA NIPA, units=billions_usd</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BEA NIPA reconstruction, units=billions_usd</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>, units=billions_usd</t>
         </is>
       </c>
     </row>
@@ -497,6 +509,16 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>S607-EXT</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>S607-RECON-A</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>S607-RECON-COMBINED</t>
         </is>
       </c>
     </row>
@@ -505,13 +527,19 @@
         <v>1952</v>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-13.7445</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>-13.7445</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E3" s="3" t="n">
         <v>-9.519399999999999</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-9.519399999999999</v>
-      </c>
-      <c r="D3" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="4">
@@ -519,13 +547,19 @@
         <v>1953</v>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-12.6252</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>-12.6252</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E4" s="3" t="n">
         <v>-9.2491</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-9.2491</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="5">
@@ -533,13 +567,19 @@
         <v>1954</v>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-8.3748</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>-8.3748</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>-6.8436</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>-6.8436</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="6">
@@ -547,13 +587,19 @@
         <v>1955</v>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-11.296</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>-11.296</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E6" s="3" t="n">
         <v>-9.8369</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-9.8369</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -561,13 +607,19 @@
         <v>1956</v>
       </c>
       <c r="B7" s="3" t="n">
+        <v>-12.237</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>-12.237</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E7" s="3" t="n">
         <v>-13.5444</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-13.5444</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="8">
@@ -575,13 +627,19 @@
         <v>1957</v>
       </c>
       <c r="B8" s="3" t="n">
+        <v>-10.3104</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>-10.3104</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E8" s="3" t="n">
         <v>-13.0864</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>-13.0864</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="9">
@@ -589,13 +647,19 @@
         <v>1958</v>
       </c>
       <c r="B9" s="3" t="n">
+        <v>-5.1952</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>-5.1952</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E9" s="3" t="n">
         <v>-7.0645</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>-7.0645</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="10">
@@ -603,13 +667,19 @@
         <v>1959</v>
       </c>
       <c r="B10" s="3" t="n">
+        <v>-8.437200000000001</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>-8.437200000000001</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E10" s="3" t="n">
         <v>-13.5535</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>-13.5535</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="11">
@@ -617,13 +687,19 @@
         <v>1960</v>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-11.8664</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-11.8664</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E11" s="3" t="n">
         <v>-19.0405</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>-19.0405</v>
-      </c>
-      <c r="D11" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -631,13 +707,19 @@
         <v>1961</v>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-6.1112</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>-6.1112</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E12" s="3" t="n">
         <v>-16.0051</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-16.0051</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="13">
@@ -645,13 +727,19 @@
         <v>1962</v>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-9.8226</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>-9.8226</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E13" s="3" t="n">
         <v>-19.4895</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-19.4895</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="14">
@@ -659,13 +747,19 @@
         <v>1963</v>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-13.8208</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>-13.8208</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E14" s="3" t="n">
         <v>-22.5453</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-22.5453</v>
-      </c>
-      <c r="D14" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="15">
@@ -673,13 +767,19 @@
         <v>1964</v>
       </c>
       <c r="B15" s="3" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-8.1</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E15" s="3" t="n">
         <v>-20.5788</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-20.5788</v>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="16">
@@ -687,13 +787,19 @@
         <v>1965</v>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-7.9964</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-7.9964</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E16" s="3" t="n">
         <v>-21.544</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-21.544</v>
-      </c>
-      <c r="D16" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="17">
@@ -701,13 +807,19 @@
         <v>1966</v>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-13.2885</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>-13.2885</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E17" s="3" t="n">
         <v>-26.599</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>-26.599</v>
-      </c>
-      <c r="D17" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="18">
@@ -715,13 +827,19 @@
         <v>1967</v>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-9.510400000000001</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>-9.510400000000001</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E18" s="3" t="n">
         <v>-21.9719</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-21.9719</v>
-      </c>
-      <c r="D18" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="19">
@@ -729,13 +847,19 @@
         <v>1968</v>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-15.7416</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>-15.7416</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E19" s="3" t="n">
         <v>-26.3708</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-26.3708</v>
-      </c>
-      <c r="D19" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="20">
@@ -743,13 +867,19 @@
         <v>1969</v>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-28.9185</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-28.9185</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E20" s="3" t="n">
         <v>-37.3993</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-37.3993</v>
-      </c>
-      <c r="D20" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="21">
@@ -757,13 +887,19 @@
         <v>1970</v>
       </c>
       <c r="B21" s="3" t="n">
+        <v>-12.3658</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>-12.3658</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E21" s="3" t="n">
         <v>-23.682</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-23.682</v>
-      </c>
-      <c r="D21" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="22">
@@ -771,13 +907,19 @@
         <v>1971</v>
       </c>
       <c r="B22" s="3" t="n">
+        <v>6.5937</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>6.5937</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E22" s="3" t="n">
         <v>-11.5875</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-11.5875</v>
-      </c>
-      <c r="D22" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="23">
@@ -785,13 +927,19 @@
         <v>1972</v>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-7.2624</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-7.2624</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E23" s="3" t="n">
         <v>-22.4084</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-22.4084</v>
-      </c>
-      <c r="D23" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="24">
@@ -799,13 +947,19 @@
         <v>1973</v>
       </c>
       <c r="B24" s="3" t="n">
+        <v>-8.128299999999999</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>-8.128299999999999</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E24" s="3" t="n">
         <v>-30.1636</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-30.1636</v>
-      </c>
-      <c r="D24" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="25">
@@ -813,13 +967,19 @@
         <v>1974</v>
       </c>
       <c r="B25" s="3" t="n">
+        <v>-8.9129</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-8.9129</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E25" s="3" t="n">
         <v>-23.6723</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-23.6723</v>
-      </c>
-      <c r="D25" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="26">
@@ -827,13 +987,19 @@
         <v>1975</v>
       </c>
       <c r="B26" s="3" t="n">
+        <v>37.9472</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>37.9472</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E26" s="3" t="n">
         <v>19.6533</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>19.6533</v>
-      </c>
-      <c r="D26" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="27">
@@ -841,13 +1007,19 @@
         <v>1976</v>
       </c>
       <c r="B27" s="3" t="n">
+        <v>21.157</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>21.157</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E27" s="3" t="n">
         <v>4.9282</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>4.9282</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="28">
@@ -855,13 +1027,19 @@
         <v>1977</v>
       </c>
       <c r="B28" s="3" t="n">
+        <v>11.7662</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>11.7662</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E28" s="3" t="n">
         <v>-9.193300000000001</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>-9.193300000000001</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="29">
@@ -869,13 +1047,19 @@
         <v>1978</v>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-13.2923</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-13.2923</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E29" s="3" t="n">
         <v>-27.1441</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-27.1441</v>
-      </c>
-      <c r="D29" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="30">
@@ -883,13 +1067,19 @@
         <v>1979</v>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-29.828</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>-29.828</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E30" s="3" t="n">
         <v>-39.7815</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-39.7815</v>
-      </c>
-      <c r="D30" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="31">
@@ -897,13 +1087,19 @@
         <v>1980</v>
       </c>
       <c r="B31" s="3" t="n">
+        <v>-16.3822</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-16.3822</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E31" s="3" t="n">
         <v>-18.4632</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>-18.4632</v>
-      </c>
-      <c r="D31" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="32">
@@ -911,13 +1107,19 @@
         <v>1981</v>
       </c>
       <c r="B32" s="3" t="n">
+        <v>-18.0741</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>-18.0741</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E32" s="3" t="n">
         <v>-41.9803</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>-41.9803</v>
-      </c>
-      <c r="D32" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="33">
@@ -925,13 +1127,19 @@
         <v>1982</v>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-19.0701</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>-19.0701</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E33" s="3" t="n">
         <v>-6.5258</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>-6.5258</v>
-      </c>
-      <c r="D33" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="34">
@@ -939,13 +1147,19 @@
         <v>1983</v>
       </c>
       <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E34" s="3" t="n">
         <v>8.991899999999999</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>8.991899999999999</v>
-      </c>
-      <c r="D34" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="35">
@@ -953,13 +1167,19 @@
         <v>1984</v>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-44.2786</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>-44.2786</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E35" s="3" t="n">
         <v>-28.4526</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-28.4526</v>
-      </c>
-      <c r="D35" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="36">
@@ -967,13 +1187,19 @@
         <v>1985</v>
       </c>
       <c r="B36" s="3" t="n">
+        <v>-71.0265</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>-71.0265</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E36" s="3" t="n">
         <v>-42.7725</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>-42.7725</v>
-      </c>
-      <c r="D36" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="37">
@@ -981,13 +1207,19 @@
         <v>1986</v>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-50.228</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>-50.228</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E37" s="3" t="n">
         <v>-41.3038</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>-41.3038</v>
-      </c>
-      <c r="D37" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="38">
@@ -995,13 +1227,19 @@
         <v>1987</v>
       </c>
       <c r="B38" s="3" t="n">
+        <v>-80.682</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>-80.682</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E38" s="3" t="n">
         <v>-76.6251</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>-76.6251</v>
-      </c>
-      <c r="D38" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="39">
@@ -1009,13 +1247,19 @@
         <v>1988</v>
       </c>
       <c r="B39" s="3" t="n">
+        <v>-87.15300000000001</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>-87.15300000000001</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E39" s="3" t="n">
         <v>-94.29219999999999</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>-94.29219999999999</v>
-      </c>
-      <c r="D39" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="40">
@@ -1023,13 +1267,19 @@
         <v>1989</v>
       </c>
       <c r="B40" s="3" t="n">
+        <v>-123.16</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>-123.16</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="E40" s="3" t="n">
         <v>-101.0163</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>-101.0163</v>
-      </c>
-      <c r="D40" s="3" t="n">
-        <v/>
       </c>
     </row>
     <row r="41">
@@ -1045,6 +1295,12 @@
       <c r="D41" s="3" t="n">
         <v>-74.7038</v>
       </c>
+      <c r="E41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>-74.7038</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1059,6 +1315,12 @@
       <c r="D42" s="3" t="n">
         <v>-11.1499</v>
       </c>
+      <c r="E42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>-11.1499</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1073,6 +1335,12 @@
       <c r="D43" s="3" t="n">
         <v>35.0773</v>
       </c>
+      <c r="E43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>35.0773</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1087,6 +1355,12 @@
       <c r="D44" s="3" t="n">
         <v>38.6308</v>
       </c>
+      <c r="E44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>38.6308</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1101,6 +1375,12 @@
       <c r="D45" s="3" t="n">
         <v>4.2275</v>
       </c>
+      <c r="E45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>4.2275</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -1115,6 +1395,12 @@
       <c r="D46" s="3" t="n">
         <v>6.0421</v>
       </c>
+      <c r="E46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>6.0421</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -1129,6 +1415,12 @@
       <c r="D47" s="3" t="n">
         <v>-31.0235</v>
       </c>
+      <c r="E47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>-31.0235</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -1143,6 +1435,12 @@
       <c r="D48" s="3" t="n">
         <v>-95.5714</v>
       </c>
+      <c r="E48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>-95.5714</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -1157,6 +1455,12 @@
       <c r="D49" s="3" t="n">
         <v>-169.4546</v>
       </c>
+      <c r="E49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>-169.4546</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -1171,6 +1475,12 @@
       <c r="D50" s="3" t="n">
         <v>-207.8886</v>
       </c>
+      <c r="E50" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>-207.8886</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -1185,6 +1495,12 @@
       <c r="D51" s="3" t="n">
         <v>-261.4047</v>
       </c>
+      <c r="E51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>-261.4047</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -1199,6 +1515,12 @@
       <c r="D52" s="3" t="n">
         <v>-145.1438</v>
       </c>
+      <c r="E52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>-145.1438</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -1213,6 +1535,12 @@
       <c r="D53" s="3" t="n">
         <v>92.91030000000001</v>
       </c>
+      <c r="E53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>92.91030000000001</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -1227,6 +1555,12 @@
       <c r="D54" s="3" t="n">
         <v>176.8911</v>
       </c>
+      <c r="E54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>176.8911</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -1241,6 +1575,12 @@
       <c r="D55" s="3" t="n">
         <v>185.1368</v>
       </c>
+      <c r="E55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>185.1368</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -1255,6 +1595,12 @@
       <c r="D56" s="3" t="n">
         <v>118.2112</v>
       </c>
+      <c r="E56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>118.2112</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -1269,6 +1615,12 @@
       <c r="D57" s="3" t="n">
         <v>94.25579999999999</v>
       </c>
+      <c r="E57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>94.25579999999999</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -1283,6 +1635,12 @@
       <c r="D58" s="3" t="n">
         <v>104.1233</v>
       </c>
+      <c r="E58" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>104.1233</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -1297,6 +1655,12 @@
       <c r="D59" s="3" t="n">
         <v>362.7016</v>
       </c>
+      <c r="E59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>362.7016</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -1311,6 +1675,12 @@
       <c r="D60" s="3" t="n">
         <v>845.8259</v>
       </c>
+      <c r="E60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>845.8259</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -1325,6 +1695,12 @@
       <c r="D61" s="3" t="n">
         <v>957.9389</v>
       </c>
+      <c r="E61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>957.9389</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -1339,6 +1715,12 @@
       <c r="D62" s="3" t="n">
         <v>897.133</v>
       </c>
+      <c r="E62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>897.133</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -1353,6 +1735,12 @@
       <c r="D63" s="3" t="n">
         <v>823.6114</v>
       </c>
+      <c r="E63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>823.6114</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -1367,6 +1755,12 @@
       <c r="D64" s="3" t="n">
         <v>604.8994</v>
       </c>
+      <c r="E64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>604.8994</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -1381,6 +1775,12 @@
       <c r="D65" s="3" t="n">
         <v>582.0185</v>
       </c>
+      <c r="E65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>582.0185</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -1395,6 +1795,12 @@
       <c r="D66" s="3" t="n">
         <v>564.5075000000001</v>
       </c>
+      <c r="E66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>564.5075000000001</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -1409,6 +1815,12 @@
       <c r="D67" s="3" t="n">
         <v>596.3379</v>
       </c>
+      <c r="E67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>596.3379</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -1423,6 +1835,12 @@
       <c r="D68" s="3" t="n">
         <v>559.9225</v>
       </c>
+      <c r="E68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>559.9225</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -1437,6 +1855,12 @@
       <c r="D69" s="3" t="n">
         <v>608.5608000000001</v>
       </c>
+      <c r="E69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>608.5608000000001</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -1451,6 +1875,12 @@
       <c r="D70" s="3" t="n">
         <v>651.6087</v>
       </c>
+      <c r="E70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>651.6087</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -1465,6 +1895,12 @@
       <c r="D71" s="3" t="n">
         <v>1812.3714</v>
       </c>
+      <c r="E71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>1812.3714</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -1479,6 +1915,12 @@
       <c r="D72" s="3" t="n">
         <v>1804.9585</v>
       </c>
+      <c r="E72" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>1804.9585</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -1493,6 +1935,12 @@
       <c r="D73" s="3" t="n">
         <v>759.9355</v>
       </c>
+      <c r="E73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>759.9355</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -1507,6 +1955,12 @@
       <c r="D74" s="3" t="n">
         <v>1117.7296</v>
       </c>
+      <c r="E74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>1117.7296</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -1521,6 +1975,12 @@
       <c r="D75" s="3" t="n">
         <v>1234.7386</v>
       </c>
+      <c r="E75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>1234.7386</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -1533,6 +1993,12 @@
         <v>1311.031</v>
       </c>
       <c r="D76" s="3" t="n">
+        <v>1311.031</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F76" s="3" t="n">
         <v>1311.031</v>
       </c>
     </row>
@@ -1547,10 +2013,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1731,7 +2197,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S&amp;T 1994</t>
+          <t>S&amp;T 1994 Appendix N (Candidate A)</t>
         </is>
       </c>
     </row>
@@ -1755,48 +2221,52 @@
       </c>
       <c r="B18" t="inlineStr"/>
     </row>
-    <row r="19"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S607-RECON-A</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BEA NIPA reconstruction</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>S607-RECON-COMBINED</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t># S607 — Net Social Wage (NSW = B_w + G_w − T_w)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Chapter**: 5 (Section 5.9 — social accounting of taxes and transfers), Appendix N. **Important**: `Table6_3_NetSocialWage.csv` is a *project-internal* source filename, NOT the printed book Table 6.3. The book's actual Table 6.3 is "Manufacturing sector, 1970" (folio 171); the net-social-wage content is in Chapter 5 §5.9 and Appendix N (Tables N.1, N.2), with Figures 5.21–5.24 (folios 140–142).</t>
+          <t># S607 — Net Social Wage (NSW = B_w + G_w − T_w)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>**Source Table**: project-internal `Table6_3_NetSocialWage.csv`, column `nsw` (digitized from the book's Appendix N net-transfer tables)</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>**Units**: billions_usd</t>
+          <t>**Chapter**: 5 (Section 5.9 — social accounting of taxes and transfers), Appendix N. **Important**: `Table6_3_NetSocialWage.csv` is a *project-internal* source filename, NOT the printed book Table 6.3. The book's actual Table 6.3 is "Manufacturing sector, 1970" (folio 171); the net-social-wage content is in Chapter 5 §5.9 and Appendix N (Tables N.1, N.2), with Figures 5.21–5.24 (folios 140–142).</t>
         </is>
       </c>
     </row>
@@ -1804,7 +2274,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>**Period**: 1952–1989 (book; S607 extends through 2025 via the NIPA continuation)</t>
+          <t>**Source Table**: project-internal `Table6_3_NetSocialWage.csv`, column `nsw` (digitized from the book's Appendix N net-transfer tables)</t>
         </is>
       </c>
     </row>
@@ -1812,7 +2282,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Units**: billions_usd</t>
         </is>
       </c>
     </row>
@@ -1820,7 +2290,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>**Status**: validated_book_and_extension</t>
+          <t>**Period**: 1952–1989 (book; S607 extends through 2025 via the NIPA continuation)</t>
         </is>
       </c>
     </row>
@@ -1828,19 +2298,23 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>**Status**: validated_book_and_extension</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The central finding of the book's social accounting of taxes and transfers (Chapter 5 §5.9): the algebraic balance between what workers receive from the state (benefits + services) and what they pay in (taxes). NEGATIVE for most of the postwar period — workers subsidize the state, not the reverse, contradicting common 'welfare state' rhetoric. The book states this directly on folio 141: "for most of the postwar period, wage and salary earners paid more in taxes than they received in social benefit expenditures."</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -1852,7 +2326,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>## Source</t>
+          <t>The central finding of the book's social accounting of taxes and transfers (Chapter 5 §5.9): the algebraic balance between what workers receive from the state (benefits + services) and what they pay in (taxes). NEGATIVE for most of the postwar period — workers subsidize the state, not the reverse, contradicting common 'welfare state' rhetoric. The book states this directly on folio 141: "for most of the postwar period, wage and salary earners paid more in taxes than they received in social benefit expenditures."</t>
         </is>
       </c>
     </row>
@@ -1864,7 +2338,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>`data/source/book_tables/Table6_3_NetSocialWage.csv` — a project-internal digitization of the book's Appendix N net-transfer tables (Tables N.1, N.2), NOT the printed Table 6.3. Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
+          <t>## Source</t>
         </is>
       </c>
     </row>
@@ -1876,7 +2350,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>`data/source/book_tables/Table6_3_NetSocialWage.csv` — a project-internal digitization of the book's Appendix N net-transfer tables (Tables N.1, N.2), NOT the printed Table 6.3. Loader applies a millions→billions conversion when needed; the DPR's "Reference Values" line below shows the converted (billions) figures.</t>
         </is>
       </c>
     </row>
@@ -1888,7 +2362,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Loaded directly from the `nsw` column of the project-internal source CSV (which the book derives as NSW = B_w + G_w − T_w in Chapter 5 §5.9 / Appendix N). An identity check could be added against S605 + S606 − S604 — left as a follow-up. Extension via the NIPA continuation (1990–2025) re-applies the same allocation rules to current national-accounts data.</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
@@ -1900,7 +2374,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
+          <t>Loaded directly from the `nsw` column of the project-internal source CSV (which the book derives as NSW = B_w + G_w − T_w in Chapter 5 §5.9 / Appendix N). An identity check could be added against S605 + S606 − S604 — left as a follow-up. Extension via the NIPA continuation (1990–2025) re-applies the same allocation rules to current national-accounts data.</t>
         </is>
       </c>
     </row>
@@ -1912,7 +2386,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1952=-9.52B; 1989=-101.02B (still negative even in the high-spending late '80s)</t>
+          <t>## Reference Values (Validation Benchmarks)</t>
         </is>
       </c>
     </row>
@@ -1924,7 +2398,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tolerance class: `dollar_series`. Validator script: `code/V03_validators/V03_S607_net_social_wage.py`. Both endpoints PASS.</t>
+          <t>1952=-9.52B; 1989=-101.02B (still negative even in the high-spending late '80s)</t>
         </is>
       </c>
     </row>
@@ -1936,7 +2410,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>## Provenance Chain</t>
+          <t>Tolerance class: `dollar_series`. Validator script: `code/V03_validators/V03_S607_net_social_wage.py`. Both endpoints PASS.</t>
         </is>
       </c>
     </row>
@@ -1948,23 +2422,19 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>data/source/book_tables/Table6_3_NetSocialWage.csv   (project-internal name; book source = Ch5 §5.9 / Appendix N)</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S607_net_social_wage.py</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1972,7 +2442,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S607.csv</t>
+          <t>data/source/book_tables/Table6_3_NetSocialWage.csv   (project-internal name; book source = Ch5 §5.9 / Appendix N)</t>
         </is>
       </c>
     </row>
@@ -1980,7 +2450,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S607_net_social_wage.py</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S607_net_social_wage.py</t>
         </is>
       </c>
     </row>
@@ -1988,7 +2458,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S607.csv</t>
+          <t xml:space="preserve">       └── data/intermediate/S607.csv</t>
         </is>
       </c>
     </row>
@@ -1996,7 +2466,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S607_net_social_wage.py</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S607_net_social_wage.py</t>
         </is>
       </c>
     </row>
@@ -2004,19 +2474,23 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">                 └── data/final/S607.csv</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S607_net_social_wage.py</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>## Citation</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -2028,7 +2502,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 5, Section 5.9 (social accounting of taxes and transfers), Appendix N (Tables N.1, N.2), Figures 5.21–5.24. Extension built from BEA NIPA government-receipts and expenditure tables (1990–2025) using the same decomposition.</t>
+          <t>## Citation</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2514,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Chapter 5, Section 5.9 (social accounting of taxes and transfers), Appendix N (Tables N.1, N.2), Figures 5.21–5.24. Extension built from BEA NIPA government-receipts and expenditure tables (1990–2025) using the same decomposition.</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2526,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard). Provenance corrected 2026-06-11 (triage patch S607): removed fabricated "Chapter 6 — The Net Social Wage" / printed-Table-6.3 citations; book source is Chapter 5 §5.9 + Appendix N.*</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -2064,7 +2538,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>## Extension activated (2026-05-14)</t>
+          <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard). Provenance corrected 2026-06-11 (triage patch S607): removed fabricated "Chapter 6 — The Net Social Wage" / printed-Table-6.3 citations; book source is Chapter 5 §5.9 + Appendix N.*</t>
         </is>
       </c>
     </row>
@@ -2076,35 +2550,35 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>S607 now spans **1952-2025** (74 years) via concat of:</t>
+          <t>## Extension activated (2026-05-14)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>- S607-A: `Table6_3_NetSocialWage.csv` (book period, 1952-1989)</t>
-        </is>
-      </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>- S607-EXT: `Table6_3_Extended.csv` (1990-2025, same NIPA methodology)</t>
+          <t>S607 now spans **1952-2025** (74 years) via concat of:</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>- S607-A: `Table6_3_NetSocialWage.csv` (book period, 1952-1989)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>**Headline regime change**: NSW first POSITIVE in 1975 (a brief 1970s positive episode), but the *persistent* sign change is in the 1990s as transfer programs (Medicare expansion, EITC) outpaced worker tax burden. 2024 NSW = $1,234B (positive).</t>
+          <t>- S607-EXT: `Table6_3_Extended.csv` (1990-2025, same NIPA methodology)</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2590,71 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
+          <t>**Headline regime change**: NSW first POSITIVE in 1975 (a brief 1970s positive episode), but the *persistent* sign change is in the 1990s as transfer programs (Medicare expansion, EITC) outpaced worker tax burden. 2024 NSW = $1,234B (positive).</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr"/>
+      <c r="B75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>Validator V03_S607 includes a regime_change_check that flags the first positive year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr"/>
+      <c r="B77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr"/>
+      <c r="B78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>## D3 book-faithful adoption (2026-07-02)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>**S607-A is now book-faithful** (NSW = Ntrrate(Table N.2)*EC; 1964 = Table N.1 exact -8.1; dollar levels carry a 2-decimal rate-rounding band). The prior BEA-API reconstruction is preserved as **S607-RECON-A** / **S607-RECON-COMBINED** (comparison arm). S607-COMBINED splices book-faithful S607-A (1952-1989) with the reconstruction extension S607-EXT (1990-2025) across a documented **method seam** at 1989/1990 (D3-DIV-NSW-SPLICE-SEAM; jump +48.46 bn; NOT re-scaled). Book-faithful NSW is positive (countercyclical) in 1971/1975/1976/1977.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>&gt; Decision: ADOPT NSW Candidate A (Appendix N Tables N.1/N.2 verbatim, 1952-1989) as book-period primary; BEA-API reconstruction becomes the labeled comparison/extension arm. Nothing deleted (.pre_d3 backups + -RECON subseries). See Handoffs/REVIEW_2026-07/D3_REGISTRY_PATCHES.json + D3_DIV_PATCHES.json.</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3600,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{"1952": -9.5194, "1989": -101.0163}</t>
+          <t>{"1964": -8.1}</t>
         </is>
       </c>
     </row>
